--- a/target_data.xlsx
+++ b/target_data.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABCD\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854F01C4-94B5-471E-A2BE-F3368719C216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19420" windowHeight="11020" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -19,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$208</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="7">
   <si>
     <t>code</t>
   </si>
@@ -61,7 +55,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -86,7 +80,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,11 +103,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -139,6 +144,7 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,21 +417,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E222"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E223"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="8"/>
+    <col min="1" max="1" width="9.1796875" style="8"/>
     <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4420,6 +4426,24 @@
         <v>5</v>
       </c>
       <c r="E222" s="3">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="8">
+        <v>2539</v>
+      </c>
+      <c r="B223" s="8">
+        <v>74543913</v>
+      </c>
+      <c r="C223" s="9">
+        <f>IFERROR(VLOOKUP(A223,Sheet2!$A:$B,2,FALSE),0)</f>
+        <v>83084984.569999993</v>
+      </c>
+      <c r="D223" t="s">
+        <v>5</v>
+      </c>
+      <c r="E223" s="3">
         <v>46112</v>
       </c>
     </row>
@@ -4431,12 +4455,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAEE2F7-1732-49D2-AEE8-DF5C62760C3B}">
-  <dimension ref="A1:B318"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B319"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6977,6 +7001,14 @@
         <v>83084984.569999993</v>
       </c>
     </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="11">
+        <v>2539</v>
+      </c>
+      <c r="B319" s="9">
+        <v>83084984.569999993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
